--- a/veterinarian_forms/026_veterinary_patient_record_efficiency_survey--veterinarian_forms.xlsx
+++ b/veterinarian_forms/026_veterinary_patient_record_efficiency_survey--veterinarian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +443,7 @@
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Is</t>
+          <t>Rating2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>this</t>
+          <t>Rating3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Format: Last Name, First Name</t>
+          <t>Format - Last Name, First Name</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
